--- a/projects/pnw-banks/pnw_banks_comp.xlsx
+++ b/projects/pnw-banks/pnw_banks_comp.xlsx
@@ -840,7 +840,7 @@
         <v>24</v>
       </c>
       <c r="B23" s="7">
-        <v>0.05</v>
+        <v>0.0492</v>
       </c>
       <c r="C23" s="7">
         <v>0.0309</v>
